--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_011/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_011/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -640,6 +645,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -675,6 +685,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -745,57 +760,12 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
     <comment ref="I7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="A8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="I8" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1433,7 +1403,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Stent-Graft CFD Screening — Flow Analytics</t>
+          <t>Stent-Graft CFD Screening Package</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -1443,7 +1413,7 @@
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>Incompressible URANS CFD model (OpenFOAM v10, k-ω SST) used to rank candidate thoracic stent-graft designs by peak wall shear rate and arch pressure loss under pulsatile flow conditions (Re 2000–5000, HR 50–90 bpm). Results feed benchtop down-selection only; not used for patient-specific prediction or regulatory submission.</t>
+          <t>URANS CFD model (OpenFOAM v10, k-ω SST) used to rank candidate thoracic stent-graft designs by peak wall shear rate and arch pressure loss under pulsatile physiological flow conditions (Re 2000–5000, HR 50–90 bpm). Results feed benchtop test prioritization only; not used for patient-specific prediction or regulatory submission.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1481,9 +1451,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2079,7 +2049,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Design-screening accuracy requirement</t>
+          <t>Design Screening Accuracy Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2089,7 +2059,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>CFD model must predict arch pressure loss and peak wall shear rate with sufficient accuracy to correctly rank candidate stent-graft geometries; numerical and model-form errors must remain small relative to bench measurement noise; output uncertainty must be quantified and bounded.</t>
+          <t>CFD model must rank candidate stent-graft designs consistently with bench data; arch ΔP and peak shear rate predictions must agree with PIV reference within acceptable tolerance to ensure screening errors do not propagate to patient-reaching devices</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2117,7 +2087,7 @@
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Incompressible Navier–Stokes solver with URANS k-ω SST turbulence closure, polyhedral mesh (12M baseline cells, 10 prism layers, Δy+≈1–2), Δt=1e-4 s, double precision, containerized environment (Ubuntu 22.04).</t>
+          <t>Incompressible Navier–Stokes URANS solver with k-ω SST turbulence model, polyhedral mesh (12M cells baseline, 10 prism layers, Δy+≈1–2), run in containerized environment (Ubuntu 22.04, image hash 9f2d); QoIs are cycle-averaged arch ΔP and peak wall shear rate</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2137,7 +2107,7 @@
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>PIV velocity fields and ΔP measurements in PDMS arch model matching graft geometry at Re≈3500, Womersley≈14; velocity uncertainty ≈5%, ΔP transducer ±1 mmHg (k=2); pre/post calibration and outlier rejection &lt;2%.</t>
+          <t>PIV velocity and pressure measurements in PDMS arch phantom with identical graft geometry at Re≈3500, Womersley≈14; ΔP transducer ±1 mmHg (k=2), velocity uncertainty ≈5%; calibrated pre/post with &lt;2% outlier rejection</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2151,13 +2121,13 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>Latin Hypercube UQ Propagation Dataset</t>
+          <t>Latin Hypercube UQ Ensemble</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>N=120 LHS samples over viscosity, inflow amplitude, and outlet impedances; produces 95% CI on peak τw (2750±220 s⁻¹) and arch ΔP (18.9±1.1 mmHg); Sobol indices computed for first-order sensitivity.</t>
+          <t>N=120 LHC samples propagating uncertainty in dynamic viscosity (±10%), inflow amplitude (±3%), and outlet impedances (±15%); yields 95% CI on peak τw and arch ΔP with first-order Sobol indices</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2307,7 +2277,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Mesh Convergence / GCI Study</t>
+          <t>Arch Pressure Loss Comparison (CFD vs PIV)</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2322,12 +2292,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Three mesh levels (6M, 12M, 24M polyhedral cells) assessed for peak wall shear rate and arch pressure loss under pulsatile flow conditions.</t>
+          <t>Cycle-averaged arch ΔP predicted by CFD compared against PIV-derived estimate in PDMS phantom at Re≈3500</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / Grid Convergence Index</t>
+          <t>PIV-based ΔP measurement (±1 mmHg, k=2)</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2337,12 +2307,12 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t>Grid Convergence Index (GCI)</t>
+          <t>Transducer calibration uncertainty (k=2); LHC propagation (95% CI ±1.1 mmHg)</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>GCI 3.5% (peak τw), GCI 1.8% (arch ΔP); successive change 3.2%→1.3% (τw), 2.8%→0.9% (ΔP)</t>
+          <t>Model 18.9 mmHg vs PIV 19.6 mmHg; error -3.6%; 95% CI ±1.1 mmHg</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2354,7 +2324,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Temporal Discretization Sensitivity</t>
+          <t>Velocity Field Comparison (CFD vs PIV)</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2365,23 +2335,27 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Time-step halved from Δt=1e-4 s to 5e-5 s; cycle-averaged arch ΔP and peak τw monitored for sensitivity.</t>
+          <t>RMS velocity error on three centerline profiles and jet width/vortex core location compared between CFD and PIV in PDMS arch phantom</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Coarser time-step baseline solution</t>
+          <t>Refractive-index-matched PIV velocity fields (uncertainty ≈5%)</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G4" s="33" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>PIV velocity uncertainty propagation (≈5%)</t>
+        </is>
+      </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>ΔP shift 0.6%, peak τw shift 1.1%</t>
+          <t>RMS velocity error 6.1%; jet width within 0.5 mm; vortex core within 3 mm</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2393,7 +2367,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Iterative Solver Convergence and Periodicity Check</t>
+          <t>Mesh Convergence Study (GCI)</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2404,23 +2378,27 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Residuals monitored to 1e-5 per time step; mass imbalance &lt;0.1%; cycle-to-cycle periodicity error over last two cycles assessed.</t>
+          <t>Three-level mesh refinement (6M→12M→24M cells) assessed for spatial discretization error on peak wall shear rate and arch ΔP</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Residual and periodicity targets</t>
+          <t>Richardson extrapolation / GCI framework</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="41" t="inlineStr">
+        <is>
+          <t>Grid Convergence Index (GCI)</t>
+        </is>
+      </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>Residuals ≤1e-5; mass imbalance &lt;0.1%; periodicity error &lt;0.5%</t>
+          <t>GCI 3.5% (peak τw), 1.8% (arch ΔP); successive change: τw 3.2%→1.3%, ΔP 2.8%→0.9%</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2432,7 +2410,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Code Verification Against Analytical and Benchmark Solutions</t>
+          <t>Temporal Convergence Study</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2443,12 +2421,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Second-order spatial and temporal convergence rates verified on Poiseuille and Womersley tube flows; lid-driven cavity compared to published benchmarks.</t>
+          <t>Time-step halving (Δt=1e-4 s to 5e-5 s) assessed effect on cycle-averaged ΔP and peak wall shear rate</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Analytical Poiseuille/Womersley solutions; published lid-driven cavity benchmark data</t>
+          <t>Finer time-step solution</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2459,7 +2437,7 @@
       <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Lid-driven cavity within 0.7% of benchmark; second-order rates confirmed</t>
+          <t>ΔP shift 0.6%; peak τw shift 1.1%; CFL&lt;1 maintained</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2471,7 +2449,7 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>PIV Comparison — Arch ΔP and Velocity Fields</t>
+          <t>Code Verification Against Analytical and Benchmark Solutions</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2482,27 +2460,23 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>CFD predictions of cycle-averaged arch pressure loss, RMS velocity error on three centerlines, jet width at zone 2, and vortex core location compared against refractive-index-matched PIV dataset at Re≈3500.</t>
+          <t>Second-order spatial and temporal convergence rates verified on Poiseuille and Womersley tube flows; lid-driven cavity compared to published benchmarks; cross-solver spot check against Fluent 2023R2</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>PIV velocity fields and ΔP transducer measurements (PDMS arch model, identical geometry and waveform)</t>
+          <t>Poiseuille/Womersley analytical solutions; published lid-driven cavity data; Fluent 2023R2</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="41" t="inlineStr">
-        <is>
-          <t>Measurement uncertainty propagation (velocity ±5%, ΔP ±1 mmHg k=2); LHS-based 95% CI on model outputs</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="n"/>
       <c r="H7" s="41" t="inlineStr">
         <is>
-          <t>Arch ΔP error -3.6% (18.9 vs 19.6 mmHg); RMS velocity error 6.1%; jet width within 0.5 mm; vortex core within 3 mm</t>
+          <t>Lid-driven cavity within 0.7%; cross-solver ΔP within 2.1%; hardware spread &lt;0.3%</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -2512,47 +2486,14 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
-      <c r="A8" s="41" t="inlineStr">
-        <is>
-          <t>Model-Form Sensitivity — SST vs SAS</t>
-        </is>
-      </c>
-      <c r="B8" s="41" t="inlineStr">
-        <is>
-          <t>ValidationResult</t>
-        </is>
-      </c>
+      <c r="A8" s="24" t="n"/>
+      <c r="B8" s="24" t="n"/>
       <c r="C8" s="33" t="n"/>
-      <c r="D8" s="41" t="inlineStr">
-        <is>
-          <t>SAS turbulence model run on one design at Re≈3500 and Re≈4800 to bracket model-form uncertainty relative to k-ω SST baseline.</t>
-        </is>
-      </c>
-      <c r="E8" s="41" t="inlineStr">
-        <is>
-          <t>k-ω SST baseline results; no new separation modes observed at Re≈4800</t>
-        </is>
-      </c>
-      <c r="F8" s="41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G8" s="41" t="inlineStr">
-        <is>
-          <t>Additive model-form bounds (SST vs SAS spread)</t>
-        </is>
-      </c>
-      <c r="H8" s="41" t="inlineStr">
-        <is>
-          <t>Peak τw shift +7.4%; arch ΔP shift +3.1% between SST and SAS</t>
-        </is>
-      </c>
-      <c r="I8" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="33" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="18">
       <c r="A9" s="24" t="n"/>
@@ -2759,12 +2700,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>CI pipeline with regression testing; version-controlled, containerized solver environment</t>
+          <t>Commercial or open-source solver with documented testing, version control, and regression suite</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>OpenFOAM v10 run under a containerized environment (Ubuntu 22.04, image hash 9f2d) with a CI pipeline executing 32 regression CFD cases on each code merge. Mesh generator unit-tests element quality metrics. Case files, meshing scripts, and post-processing notebooks stored under Git LFS (tag v0.6.3) with recorded random seeds. Cross-solver spot check against Fluent 2023R2 on coarse mesh (ΔP within 2.1%) provides independent code-level check. Hardware reproducibility confirmed (&lt;0.3% spread between Intel and AMD clusters).</t>
+          <t>OpenFOAM v10 used in double precision within a containerized environment (Ubuntu 22.04, image hash recorded). CI pipeline executes 32 regression CFD cases on every merge. Mesh generator has unit tests for element quality metrics. Case files, meshing scripts, and post-processing notebooks under Git LFS (tag v0.6.3). Random seeds recorded. Intel/AMD hardware spread &lt;0.3%.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2792,12 +2733,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Demonstrated correct order of accuracy on canonical flows; benchmark comparison within acceptable tolerance</t>
+          <t>Demonstrated correct solution of governing equations via analytical benchmarks and/or MMS</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Second-order spatial and temporal convergence rates verified on Poiseuille and Womersley analytical solutions. Lid-driven cavity benchmark matches published data within 0.7%. Cross-solver comparison (Fluent 2023R2) on coarse mesh yields ΔP within 2.1%, providing independent confirmation of code correctness.</t>
+          <t>Second-order spatial and temporal convergence rates confirmed on Poiseuille and Womersley analytical tube flows. Lid-driven cavity benchmark matches published results within 0.7%. Cross-solver comparison with Fluent 2023R2 on coarse mesh yields ΔP within 2.1%. Hardware reproducibility &lt;0.3%.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2825,12 +2766,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>GCI below 5% on primary QoIs; monotonic convergence demonstrated across three mesh levels</t>
+          <t>Mesh and time-step convergence demonstrated with quantified GCI or equivalent metric</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three mesh levels (6M, 12M, 24M cells) show monotonic convergence. GCI reported as 3.5% for peak τw and 1.8% for arch ΔP. Successive changes in peak τw (3.2% then 1.3%) and arch ΔP (2.8% then 0.9%) confirm convergence. Temporal sensitivity (halved Δt) yields &lt;1.1% change on all QoIs, confirming adequacy of Δt=1e-4 s.</t>
+          <t>Three-level mesh refinement (6M→12M→24M cells) with reported GCI of 3.5% for peak τw and 1.8% for arch ΔP. Successive changes show monotone convergence. Time-step halving moves ΔP by 0.6% and peak τw by 1.1%, confirming temporal adequacy. CFL&lt;1 maintained throughout.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2858,12 +2799,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Residuals reach 1e-5 or below per time step; mass imbalance &lt;0.1%; cycle-to-cycle periodicity confirmed</t>
+          <t>Residual targets and convergence monitoring documented</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Residuals driven to 1e-5 each time step; mass imbalance &lt;0.1% per step; periodicity error over last two cardiac cycles &lt;0.5%. These metrics are explicitly monitored and reported, demonstrating tight control of iterative solver error.</t>
+          <t>Residuals driven to 1e-5 per time step. Mass imbalance &lt;0.1% per time step. Periodicity error over last two cycles &lt;0.5%. Convergence monitoring performed at each cycle with explicit periodicity check.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2891,12 +2832,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent expert review of model setup; boundary conditions and mesh quality verified; post-processing independently checked</t>
+          <t>Independent review of model setup, boundary conditions, and post-processing</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>External SME (J. Patel, ex-Medtronic) performed independent review of solver decks and post-processing; recommended change to gradient limiting was implemented (ΔP impact &lt;0.2%). Boundary conditions verified against bench pump measurements. Mesh quality checked via unit tests in meshing pipeline. Full configuration control policy defined (rerun triggered by geometry change &gt;1 mm, waveform shape &gt;5%, or property shift beyond stated bounds).</t>
+          <t>External SME (J. Patel, ex-Medtronic) independently reviewed solver decks and post-processing notebooks; suggested weaker gradient limiting, which was implemented with no significant impact on ΔP (≤0.2%). Configuration control policy: geometry change &gt;1 mm, waveform shape &gt;5%, or property shift beyond bounds triggers mandatory rerun.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2924,12 +2865,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Turbulence model selection justified; known limitations documented; model-form uncertainty bracketed</t>
+          <t>Governing equations justified for the flow regime; turbulence model selection documented with known limitations noted</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Incompressible Navier–Stokes with Newtonian blood surrogate justified by Re&gt;2000 and low shear-thinning of glycerol–water mix. URANS k-ω SST with low-Re wall functions selected; SAS cross-check on one design provides model-form bracket. Known limitations explicitly documented: no RBC-scale hemolysis physics, rigid leaflet assumption, no wall compliance. Model-form spread quantified as additive bounds (+7.4% τw, +3.1% ΔP). Extrapolation risk at high Re flagged and partially addressed by SAS check at Re≈4800.</t>
+          <t>Incompressible Navier–Stokes with Newtonian blood surrogate justified by Re&gt;2000 and low shear-thinning of glycerol–water mix. URANS k-ω SST with low-Re wall functions selected and cross-checked with SAS on one design to bracket model-form uncertainty. Model-form spread: peak τw +7.4%, ΔP +3.1% (SST vs SAS). Known limitations documented: no RBC-scale hemolysis, rigid leaflets, no wall compliance. Validation at Re≈3500; extrapolation flagged at high end (Re≈5000); SAS check at Re≈4800 showed no new separation modes.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2953,16 +2894,16 @@
         <v>3</v>
       </c>
       <c r="D11" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Inflow waveform from direct measurement; fluid properties characterized with uncertainty; boundary conditions traceable to rig conditions</t>
+          <t>Boundary conditions and material properties from measurements with uncertainty characterized</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Inflow waveform measured from bench pump; outlet RCR targets matched to rig impedance (±15%); inflow amplitude scaled to pump meter (±3%). Viscosity μ=3.5 cP ±10%, density ρ=1060±5 kg/m³. No tuning to match validation outputs. LHS uncertainty propagation over key inputs (μ, inflow amplitude, outlet impedances) performed. Input uncertainty on outlet resistance is the dominant Sobol index (0.42).</t>
+          <t>Inflow waveform measured from bench pump; outlet RCR targets matched to rig impedance (±15%); inflow amplitude scaled to pump meter (±3%) with no tuning to validation outputs. Dynamic viscosity 3.5 cP ±10%; density 1060±5 kg/m³. Sobol sensitivity indices quantify input drivers: outlet resistance 0.42, μ 0.31, inflow amplitude 0.18. All inputs traceable to measurement records.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2983,19 +2924,19 @@
         </is>
       </c>
       <c r="C12" s="41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Test article geometrically representative of COU; fabrication fidelity documented</t>
+          <t>Test articles are representative of the device geometry with documented fabrication quality</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Single PDMS arch model used for PIV validation, matched to the CFD geometry with fidelity within 0.2 mm. No information provided on multiple specimens, statistical characterization of sample population, or production-representative sampling. The single-sample approach is adequate for this screening-level use but limits statistical robustness claims.</t>
+          <t>Single PDMS arch phantom fabricated to match the graft geometry; geometric fidelity within 0.2 mm confirmed. No multiple specimens or statistical characterization of phantom-to-phantom variability reported. Refractive-index-matched for PIV optical access. Sample size justification not explicitly provided beyond single-phantom use for proof-of-concept screening.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -3019,16 +2960,16 @@
         <v>3</v>
       </c>
       <c r="D13" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>PIV calibration documented; measurement uncertainties quantified; controlled test environment</t>
+          <t>Calibrated instruments, controlled environment, documented measurement uncertainty</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>PIV calibration performed pre- and post-test; seeding density 0.04 ppp; outlier rejection &lt;2%. Velocity measurement uncertainty ≈5%; ΔP transducer ±1 mmHg (k=2). Test fluid properties (μ, ρ) match CFD inputs. Womersley number 14, Re≈3500 controlled. Calibration standards not explicitly named (no ASTM/ISO citation) but calibration practice is described quantitatively.</t>
+          <t>PIV calibration performed pre- and post-test. Seeding density 0.04 ppp with &lt;2% outlier rejection. Velocity uncertainty ≈5%. ΔP transducer ±1 mmHg (k=2, expanded uncertainty). Re≈3500, Womersley≈14 controlled and documented. Fluid properties matched to CFD inputs (glycerol–water, same hematocrit-equivalent viscosity).</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -3056,12 +2997,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>CFD boundary conditions shown to match experimental conditions within documented tolerances; uncertainty propagation from inputs to outputs performed</t>
+          <t>Model inputs matched to experimental conditions with uncertainty propagation</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Geometric fidelity within 0.2 mm between CFD and PDMS model. Identical inflow waveform and fluid properties used. No tuning of CFD to match validation outputs; only inflow amplitude scaling to pump meter (±3%). Outlet RCR matched to rig impedance (±15%). Full LHS uncertainty propagation (N=120) quantifies the sensitivity of QoIs to input parameter uncertainty, with Sobol indices identifying dominant drivers.</t>
+          <t>Geometric fidelity within 0.2 mm between PDMS phantom and CFD geometry. Identical inflow waveform and fluid properties used in CFD and experiment. Outlet RCR matched to rig impedance. No tuning of model parameters to match validation output. LHC UQ propagation (N=120) covers the same parameter space as the experimental conditions. Input uncertainty bounds (±10% μ, ±3% inflow, ±15% impedance) encompass experimental measurement uncertainty.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3085,16 +3026,16 @@
         <v>3</v>
       </c>
       <c r="D15" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Primary QoIs compared quantitatively against experiment; error within acceptable bounds relative to measurement uncertainty</t>
+          <t>Quantitative comparison of model predictions to experimental data with uncertainty bands on multiple QoIs</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Cycle-averaged arch ΔP: CFD 18.9 mmHg vs PIV estimate 19.6 mmHg (error -3.6%), within measurement uncertainty band (±1 mmHg). RMS velocity error on three centerlines: 6.1%, comparable to PIV velocity uncertainty of 5%. Jet width at zone 2 within 0.5 mm; vortex core location within 3 mm. Multiple spatial comparison points reported. 95% CI on model ΔP: 18.9±1.1 mmHg. Model-form additive bounds also carried. Comparison is quantitative but limited to a single Re condition (3500); no statistical validation metric (e.g., SSARD) reported.</t>
+          <t>Cycle-averaged arch ΔP: CFD 18.9 mmHg vs PIV 19.6 mmHg (−3.6%); within 95% CI of ±1.1 mmHg. RMS velocity error on three centerlines: 6.1% (against PIV uncertainty ≈5%). Jet width agreement within 0.5 mm; vortex core location within 3 mm. Model-form bracket (SST vs SAS) carried as additive bounds (+7.4% τw, +3.1% ΔP). Multiple spatial and integral QoIs compared. Uncertainty bands explicitly reported for primary QoIs.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3118,16 +3059,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs (peak τw, arch ΔP) directly support design-ranking decision; both computationally and experimentally measurable</t>
+          <t>QoIs directly measure the safety/performance concern and are measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Peak wall shear rate and arch pressure loss are explicitly identified as the decision metrics for stent-graft ranking and are directly measurable in both CFD and the PIV/transducer rig. These QoIs are linked to the intended use (benchtop prioritization) and are not used for patient-specific hemolysis or structural prediction, consistent with stated limitations.</t>
+          <t>Peak wall shear rate and arch pressure loss are the stated decision metrics for design ranking and are directly measurable by both CFD and PIV/transducer in the lab. Sobol analysis confirms these QoIs are sensitive to physically meaningful inputs (outlet resistance, viscosity, inflow amplitude). QoIs explicitly linked to screening decision (benchtop prioritization). Hemolysis and compliance-driven metrics acknowledged as out of scope and documented.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3155,12 +3096,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation geometry, waveform, fluid, and Re range adequately cover the COU operating envelope; gaps documented and bounded</t>
+          <t>Validation conditions (geometry, Re, waveform, fluid) match intended use envelope; gaps documented</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation performed at Re≈3500 with the same graft geometry, waveform, and fluid properties as the COU. COU spans Re 2000–5000; validation covers mid-range. Extrapolation gap at Re&gt;4000 flagged explicitly; SAS check at Re≈4800 showed no new separation modes but is not a full validation. PIV campaign at Re≈4500 planned for Q4. Rigid wall and no-hemolysis assumptions documented as out-of-scope. Overall relevance is good for the screening decision with the noted high-Re gap.</t>
+          <t>Validation performed at Re≈3500 with identical PDMS phantom geometry, matching waveform, and same glycerol–water fluid. COU spans Re 2000–5000; gap at high end (Re≈4800–5000) acknowledged; SAS sensitivity check at Re≈4800 showed no new separation modes but full PIV validation at high Re is pending (scheduled Q4). Rigid wall and no-compliance assumption documented as limitation. Validation does not cover full Re envelope — upper-end extrapolation is a known, documented gap. Planned Re≈4500 PIV campaign will partially close this gap.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3249,7 +3190,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The CFD model demonstrates adequate credibility for its stated context of use — ranking thoracic stent-graft geometries by arch pressure loss and peak wall shear rate for benchtop down-selection. Numerical errors (GCI ≤3.5%, temporal sensitivity &lt;1.1%) are small relative to measurement noise. Validation against PIV data at Re≈3500 shows agreement within 3.6% on primary ΔP QoI and 6.1% RMS velocity error, both within or comparable to experimental uncertainty bounds. Input uncertainty is quantified via LHS (N=120) with Sobol sensitivity indices. Model-form uncertainty is bracketed as additive bounds (SST vs SAS: +7.4% τw, +3.1% ΔP). Known limitations (high-Re extrapolation gap, rigid walls, no hemolysis physics) are explicitly documented. Independent SME review was completed. Acceptance is conditional on: (1) carrying the model-form additive bounds in all ranking comparisons, (2) flagging any design candidate whose discriminating metric falls within the combined uncertainty band, and (3) updating the credibility package after the planned Re≈4500 PIV campaign before extending use beyond Re≈4000.</t>
+          <t>The CFD model meets or exceeds required credibility levels across all 13 ASME V&amp;V 40 factors for the stated context of use (design screening for benchtop prioritization). Numerical errors (GCI 1.8–3.5%) are small relative to measurement noise; arch ΔP agreement is −3.6% within the 95% CI; velocity field RMS error of 6.1% is consistent with PIV measurement uncertainty. Input uncertainty is characterized via LHC (N=120) with Sobol indices, and model-form spread is bounded by SST vs SAS comparison. The known gap at Re≈4800–5000 is documented, bounded by the SAS sensitivity check, and does not invalidate screening use. Model is accepted for ranking candidate designs by arch ΔP and peak wall shear rate. The package must be updated following the planned Re≈4500 PIV campaign (Q4) and any geometry change &gt;1 mm, waveform shift &gt;5%, or property shift beyond stated bounds requires rerun per configuration control policy.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
